--- a/Data Files/6.2. Akun Enquiry - Bank Tujuan Sedang Tidak Aktif.xlsx
+++ b/Data Files/6.2. Akun Enquiry - Bank Tujuan Sedang Tidak Aktif.xlsx
@@ -1,31 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wirafidi/git/Bifast-2.0-Katalon/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7758605-CF5F-4A8E-9FCA-59D75D60494B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6FBDE1-B35F-F849-857D-41E9D7FAAC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Content_Type</t>
   </si>
@@ -33,61 +42,46 @@
     <t>transactionId</t>
   </si>
   <si>
-    <t>transactionCode</t>
-  </si>
-  <si>
-    <t>cid</t>
-  </si>
-  <si>
     <t>channelType</t>
   </si>
   <si>
+    <t>debitedAccountNumber</t>
+  </si>
+  <si>
+    <t>creditedBic</t>
+  </si>
+  <si>
+    <t>creditedProxyType</t>
+  </si>
+  <si>
+    <t>creditedProxyAlias</t>
+  </si>
+  <si>
+    <t>chargeType</t>
+  </si>
+  <si>
+    <t>trxAmount</t>
+  </si>
+  <si>
+    <t>feeAmount</t>
+  </si>
+  <si>
+    <t>amountCurrency</t>
+  </si>
+  <si>
+    <t>categoryPurpose</t>
+  </si>
+  <si>
+    <t>chargeBearerCode</t>
+  </si>
+  <si>
     <t>application/json</t>
   </si>
   <si>
-    <t>MBL</t>
-  </si>
-  <si>
-    <t>branchInput</t>
-  </si>
-  <si>
-    <t>debitedAccountNumber</t>
-  </si>
-  <si>
-    <t>creditedBic</t>
-  </si>
-  <si>
-    <t>creditedProxyType</t>
-  </si>
-  <si>
-    <t>creditedProxyAlias</t>
-  </si>
-  <si>
-    <t>chargeType</t>
-  </si>
-  <si>
-    <t>trxAmount</t>
-  </si>
-  <si>
-    <t>feeAmount</t>
-  </si>
-  <si>
-    <t>amountCurrency</t>
-  </si>
-  <si>
-    <t>categoryPurpose</t>
-  </si>
-  <si>
-    <t>chargeBearerCode</t>
-  </si>
-  <si>
-    <t>userInput</t>
-  </si>
-  <si>
-    <t>300000</t>
-  </si>
-  <si>
-    <t>0502</t>
+    <t>0019845621100</t>
+  </si>
+  <si>
+    <t>ATOSIDJ1</t>
   </si>
   <si>
     <t>00</t>
@@ -105,28 +99,19 @@
     <t>IDR</t>
   </si>
   <si>
-    <t>99</t>
-  </si>
-  <si>
     <t>DEBT</t>
   </si>
   <si>
-    <t>A002</t>
-  </si>
-  <si>
-    <t>0019845621100</t>
-  </si>
-  <si>
-    <t>FAST-JSON-MBL-01</t>
-  </si>
-  <si>
-    <t>ATOSIDJ1</t>
-  </si>
-  <si>
-    <t>400000001</t>
-  </si>
-  <si>
-    <t>250825234711</t>
+    <t>institutionBic</t>
+  </si>
+  <si>
+    <t>BMRIIDJA</t>
+  </si>
+  <si>
+    <t>KOMIMOBILE</t>
+  </si>
+  <si>
+    <t>25646534444950</t>
   </si>
 </sst>
 </file>
@@ -206,9 +191,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +231,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -352,7 +337,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -494,7 +479,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -502,116 +487,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA04E825-9583-433C-8FA8-025B5A2F7BE7}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="17" width="20.5546875" customWidth="1"/>
+    <col min="1" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="H2" s="2">
+        <v>400000001</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="M2" s="2">
+        <v>99</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
